--- a/survey_templates/036_workshop_session_quality_poll--survey_templates.xlsx
+++ b/survey_templates/036_workshop_session_quality_poll--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>introduction_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>introduction_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Was the workshop well-organized?</t>
+          <t>Content 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Was the workshop well-structured?</t>
+          <t>Content 6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Was the workshop well-organized?</t>
+          <t>Content 14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>content_17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -986,7 +986,7 @@
   <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1011,7 +1011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>introduction_choices</t>
+          <t>introduction_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>introduction_choices</t>
+          <t>introduction_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1062,7 +1062,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1096,7 +1096,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1130,7 +1130,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_9_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_9_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_10_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_10_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_11_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_11_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_12_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_12_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_13_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_13_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_14_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1436,7 +1436,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_14_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_15_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_15_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_16_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1504,7 +1504,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_16_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_16_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_16_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>content_choices</t>
+          <t>content_16_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
